--- a/attention/mixed_quant_sparse_flash_mla/tests/pytest/result.xlsx
+++ b/attention/mixed_quant_sparse_flash_mla/tests/pytest/result.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN8"/>
+  <dimension ref="A1:AN15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,6 +1621,1012 @@
         </is>
       </c>
       <c r="AN8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SWA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>64</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>512</v>
+      </c>
+      <c r="M9" t="n">
+        <v>512</v>
+      </c>
+      <c r="N9" t="n">
+        <v>65</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>128</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AN9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SWA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>64</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>512</v>
+      </c>
+      <c r="M10" t="n">
+        <v>512</v>
+      </c>
+      <c r="N10" t="n">
+        <v>65</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>128</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SWA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>64</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>512</v>
+      </c>
+      <c r="M11" t="n">
+        <v>512</v>
+      </c>
+      <c r="N11" t="n">
+        <v>65</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>128</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SWA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>64</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
+        <v>512</v>
+      </c>
+      <c r="M12" t="n">
+        <v>512</v>
+      </c>
+      <c r="N12" t="n">
+        <v>65</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>128</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SWA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>64</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>512</v>
+      </c>
+      <c r="M13" t="n">
+        <v>512</v>
+      </c>
+      <c r="N13" t="n">
+        <v>65</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>128</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SWA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>64</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>512</v>
+      </c>
+      <c r="M14" t="n">
+        <v>512</v>
+      </c>
+      <c r="N14" t="n">
+        <v>65</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>128</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>SWA</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AN14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mixedQuantSparseFlashMla_SCFA_decode_TND_BF16_PA_BBND_FP8_E4M3FN_1_64_1_1_8193_512_512_64_000000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TND</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PA_BBND</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>torch.bfloat16</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>torch.float8_e4m3fn</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>64</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>512</v>
+      </c>
+      <c r="M15" t="n">
+        <v>512</v>
+      </c>
+      <c r="N15" t="n">
+        <v>65</v>
+      </c>
+      <c r="O15" t="n">
+        <v>16</v>
+      </c>
+      <c r="P15" t="n">
+        <v>128</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>128</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>[0, 1]</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>[8193]</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>[2048]</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>[0, 8193]</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>[0, 2048]</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>[1]</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.04419417</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>127</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>SCFA</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>full</t>
+        </is>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>64</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>64</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="AN15" t="n">
         <v>100</v>
       </c>
     </row>
